--- a/downloads/Kroger-Experis-Savings-Model.xlsx
+++ b/downloads/Kroger-Experis-Savings-Model.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://manpowergroupapps-my.sharepoint.com/personal/colleen_eagleton_manpowergroup_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanlynch/Desktop/CLAUDE/Kroger Redux/site/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{685F94B2-867D-4546-B665-E1C34ACF7509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FA1552-5DBA-8043-82F7-8FA518655CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Savings Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Vendor Streamlining" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -154,12 +154,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(\$* #,##0.0,,\M_);_(\$* \(#,##0.0,,&quot;)M&quot;;_(\$* \-_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00000000000000%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,52 +171,52 @@
       <sz val="16"/>
       <color rgb="FF14152B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B6E7F"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF14152B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF6B6E7F"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -290,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -302,11 +301,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -612,89 +607,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <dimension ref="B2:G22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="21">
+    <row r="2" spans="2:7" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="6">
         <v>12000000</v>
       </c>
-      <c r="D9" s="9">
-        <v>0.628</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row r="12" spans="2:8">
+      <c r="G9" s="22"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
@@ -708,8 +697,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20.45">
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="2:7" ht="24" x14ac:dyDescent="0.2">
+      <c r="B14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="6">
@@ -718,12 +707,12 @@
       <c r="D14" s="6">
         <v>2200000</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20.45">
-      <c r="B15" s="10" t="s">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="6">
@@ -732,12 +721,12 @@
       <c r="D15" s="6">
         <v>800000</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="20.45">
-      <c r="B16" s="10" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="6">
@@ -746,57 +735,57 @@
       <c r="D16" s="6">
         <v>1000000</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="12" t="s">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="11">
         <f>SUM(C14:C16)</f>
         <v>3100000</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="11">
         <f>SUM(D14:D16)</f>
         <v>4000000</v>
       </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="2:5" ht="20.45">
-      <c r="B18" s="10" t="s">
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18" spans="2:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="B18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="14">
         <f>'Vendor Streamlining'!C16</f>
         <v>7000000</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="17" t="s">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17">
         <f>D17+D18</f>
         <v>11000000</v>
       </c>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="22" spans="2:5" ht="19.350000000000001" customHeight="1">
-      <c r="B22" s="26" t="s">
+      <c r="E20" s="16"/>
+    </row>
+    <row r="22" spans="2:5" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -810,7 +799,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -818,17 +807,17 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="21">
+    <row r="2" spans="2:4" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
@@ -836,101 +825,101 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" customHeight="1">
-      <c r="B6" s="20">
+    <row r="6" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="18">
         <v>50</v>
       </c>
       <c r="C6" s="6">
         <v>1154412</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
-      <c r="B7" s="20">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="18">
         <v>75</v>
       </c>
       <c r="C7" s="6">
         <v>1731618</v>
       </c>
-      <c r="D7" s="26"/>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="20">
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="18">
         <v>100</v>
       </c>
       <c r="C8" s="6">
         <v>2308825</v>
       </c>
-      <c r="D8" s="26"/>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" s="20">
+      <c r="D8" s="24"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="18">
         <v>125</v>
       </c>
       <c r="C9" s="6">
         <v>2886031</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
-      <c r="B10" s="20">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="18">
         <v>150</v>
       </c>
       <c r="C10" s="6">
         <v>3463238</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
-      <c r="B11" s="20">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="18">
         <v>175</v>
       </c>
       <c r="C11" s="6">
         <v>4040444</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="20">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="18">
         <v>200</v>
       </c>
       <c r="C12" s="6">
         <v>4617650</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="20">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="18">
         <v>225</v>
       </c>
       <c r="C13" s="6">
         <v>5194857</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="20">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="18">
         <v>250</v>
       </c>
       <c r="C14" s="6">
         <v>5772063</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="20">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="18">
         <v>275</v>
       </c>
       <c r="C15" s="6">
         <v>6349239</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
-      <c r="B16" s="21">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="19">
         <v>300</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="20">
         <v>7000000</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="23"/>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
